--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-evaluation-composant-n2.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-evaluation-composant-n2.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4177" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4177" uniqueCount="388">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -733,6 +733,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>Observation.statusCode</t>
@@ -6159,7 +6163,7 @@
         <v>74</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>74</v>
+        <v>234</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>74</v>
@@ -6167,10 +6171,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6196,10 +6200,10 @@
         <v>91</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6230,7 +6234,7 @@
       </c>
       <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>74</v>
@@ -6248,7 +6252,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6268,10 +6272,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6369,10 +6373,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6413,7 +6417,7 @@
         <v>74</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="T48" t="s" s="2">
         <v>74</v>
@@ -6472,10 +6476,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6575,10 +6579,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6678,10 +6682,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6781,10 +6785,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6884,10 +6888,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6985,10 +6989,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7086,10 +7090,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7189,10 +7193,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7292,10 +7296,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7395,10 +7399,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7421,13 +7425,13 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7478,7 +7482,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7498,10 +7502,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7524,7 +7528,7 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
@@ -7557,7 +7561,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>74</v>
@@ -7575,7 +7579,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7595,10 +7599,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7621,7 +7625,7 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7674,7 +7678,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7694,10 +7698,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7753,25 +7757,25 @@
       </c>
       <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF61" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7791,10 +7795,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7820,10 +7824,10 @@
         <v>141</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -7874,7 +7878,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -7894,10 +7898,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7995,10 +7999,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8098,10 +8102,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8201,10 +8205,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8304,10 +8308,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8407,10 +8411,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8510,10 +8514,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8611,10 +8615,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8712,10 +8716,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8815,10 +8819,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8916,10 +8920,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9017,10 +9021,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9120,10 +9124,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9221,10 +9225,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9324,10 +9328,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9425,10 +9429,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9522,10 +9526,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9627,10 +9631,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9730,10 +9734,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9825,7 +9829,7 @@
         <v>74</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>74</v>
+        <v>234</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>74</v>
@@ -9833,10 +9837,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9936,10 +9940,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10039,10 +10043,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10065,13 +10069,13 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -10102,7 +10106,7 @@
       </c>
       <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>74</v>
@@ -10120,7 +10124,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -10140,10 +10144,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10166,7 +10170,7 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
@@ -10199,25 +10203,25 @@
       </c>
       <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF85" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10237,10 +10241,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10267,7 +10271,7 @@
       </c>
       <c r="L86" s="2"/>
       <c r="M86" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -10318,7 +10322,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10338,10 +10342,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10364,7 +10368,7 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
@@ -10417,7 +10421,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10437,10 +10441,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10463,7 +10467,7 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -10516,7 +10520,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10536,10 +10540,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10562,7 +10566,7 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
@@ -10615,7 +10619,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10635,10 +10639,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10661,7 +10665,7 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -10714,7 +10718,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10734,10 +10738,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10760,7 +10764,7 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -10813,7 +10817,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10833,10 +10837,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10859,7 +10863,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -10912,7 +10916,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10932,10 +10936,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10958,7 +10962,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -11011,7 +11015,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -11031,10 +11035,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11132,10 +11136,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11233,10 +11237,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11334,10 +11338,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11435,10 +11439,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11538,10 +11542,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11641,10 +11645,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11744,10 +11748,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11847,10 +11851,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11877,7 +11881,7 @@
       </c>
       <c r="L102" s="2"/>
       <c r="M102" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -11948,10 +11952,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -11988,7 +11992,7 @@
         <v>74</v>
       </c>
       <c r="S103" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="T103" t="s" s="2">
         <v>74</v>
@@ -12007,7 +12011,7 @@
       </c>
       <c r="Y103" s="2"/>
       <c r="Z103" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>74</v>
@@ -12025,7 +12029,7 @@
         <v>74</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>75</v>
@@ -12045,10 +12049,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12075,7 +12079,7 @@
       </c>
       <c r="L104" s="2"/>
       <c r="M104" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -12087,7 +12091,7 @@
         <v>74</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="T104" t="s" s="2">
         <v>74</v>
@@ -12126,7 +12130,7 @@
         <v>74</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -12146,10 +12150,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12176,12 +12180,12 @@
       </c>
       <c r="L105" s="2"/>
       <c r="M105" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q105" s="2"/>
       <c r="R105" t="s" s="2">
@@ -12227,7 +12231,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -12247,10 +12251,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12326,7 +12330,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -12346,10 +12350,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12372,7 +12376,7 @@
         <v>74</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
@@ -12425,7 +12429,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -12445,10 +12449,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12471,7 +12475,7 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
@@ -12524,7 +12528,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -12544,10 +12548,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12570,7 +12574,7 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -12623,7 +12627,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -12643,10 +12647,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12669,7 +12673,7 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
@@ -12722,7 +12726,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -12742,10 +12746,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12768,7 +12772,7 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -12821,7 +12825,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -12841,10 +12845,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -12867,7 +12871,7 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -12920,7 +12924,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -12940,10 +12944,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -12966,7 +12970,7 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -13019,7 +13023,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -13039,10 +13043,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13065,7 +13069,7 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
@@ -13118,7 +13122,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -13138,10 +13142,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13164,7 +13168,7 @@
         <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
@@ -13217,7 +13221,7 @@
         <v>74</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -13237,10 +13241,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13263,7 +13267,7 @@
         <v>74</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
@@ -13316,7 +13320,7 @@
         <v>74</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -13336,10 +13340,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13362,7 +13366,7 @@
         <v>74</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L117" s="2"/>
       <c r="M117" s="2"/>
@@ -13415,7 +13419,7 @@
         <v>74</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -13435,10 +13439,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13461,7 +13465,7 @@
         <v>74</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
@@ -13514,7 +13518,7 @@
         <v>74</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -13534,10 +13538,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13560,7 +13564,7 @@
         <v>74</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L119" s="2"/>
       <c r="M119" s="2"/>
@@ -13613,7 +13617,7 @@
         <v>74</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -13633,10 +13637,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13659,7 +13663,7 @@
         <v>74</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
@@ -13712,7 +13716,7 @@
         <v>74</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -13732,10 +13736,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13758,11 +13762,11 @@
         <v>74</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L121" s="2"/>
       <c r="M121" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -13813,7 +13817,7 @@
         <v>74</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -13833,10 +13837,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13934,10 +13938,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14035,10 +14039,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14136,10 +14140,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14237,10 +14241,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14340,10 +14344,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14443,10 +14447,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14546,10 +14550,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14649,10 +14653,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -14679,7 +14683,7 @@
       </c>
       <c r="L130" s="2"/>
       <c r="M130" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -14750,10 +14754,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -14787,7 +14791,7 @@
       </c>
       <c r="Q131" s="2"/>
       <c r="R131" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="S131" t="s" s="2">
         <v>74</v>
@@ -14809,7 +14813,7 @@
       </c>
       <c r="Y131" s="2"/>
       <c r="Z131" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>74</v>
@@ -14827,7 +14831,7 @@
         <v>74</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -14847,10 +14851,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -14873,7 +14877,7 @@
         <v>74</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L132" s="2"/>
       <c r="M132" s="2"/>
@@ -14926,7 +14930,7 @@
         <v>74</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>75</v>
@@ -14946,10 +14950,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -14972,7 +14976,7 @@
         <v>74</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L133" s="2"/>
       <c r="M133" s="2"/>
@@ -15025,7 +15029,7 @@
         <v>74</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
